--- a/derivatives/BAR/P8775_preprocessed.xlsx
+++ b/derivatives/BAR/P8775_preprocessed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>listno</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>trialno</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>conceptno</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>concept</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>concept_HU</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>responded</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>response_HU</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>similarity</t>
         </is>
@@ -569,7 +581,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.820915162563324</v>
+        <v>0.8209152221679688</v>
       </c>
     </row>
     <row r="4">
@@ -903,7 +915,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.4643029272556305</v>
+        <v>0.4643030166625977</v>
       </c>
     </row>
     <row r="11">
@@ -1367,7 +1379,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.5467605590820312</v>
+        <v>0.546760618686676</v>
       </c>
     </row>
     <row r="21">
@@ -1587,7 +1599,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.1748422384262085</v>
+        <v>0.1748422533273697</v>
       </c>
     </row>
     <row r="26">
@@ -2603,7 +2615,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.6193221211433411</v>
+        <v>0.6193221807479858</v>
       </c>
     </row>
     <row r="49">
@@ -3043,7 +3055,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.4697264432907104</v>
+        <v>0.4697265028953552</v>
       </c>
     </row>
     <row r="59">
@@ -3693,7 +3705,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.2204750180244446</v>
+        <v>0.2204750031232834</v>
       </c>
     </row>
     <row r="74">
@@ -3839,7 +3851,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.7563679218292236</v>
+        <v>0.7563677430152893</v>
       </c>
     </row>
     <row r="77">
@@ -4153,7 +4165,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.3964138925075531</v>
+        <v>0.3964139521121979</v>
       </c>
     </row>
     <row r="84">
@@ -4247,7 +4259,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.134099930524826</v>
+        <v>0.1340999454259872</v>
       </c>
     </row>
     <row r="86">
@@ -4509,7 +4521,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.2442677915096283</v>
+        <v>0.2442678213119507</v>
       </c>
     </row>
     <row r="92">
@@ -4687,7 +4699,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.1047981604933739</v>
+        <v>0.1047981679439545</v>
       </c>
     </row>
     <row r="96">
